--- a/Ft-Cloud/ft-services/ft-service-pm/src/main/resources/template/importXmslContractGeneral.xlsx
+++ b/Ft-Cloud/ft-services/ft-service-pm/src/main/resources/template/importXmslContractGeneral.xlsx
@@ -1,63 +1,83 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26529"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\25757\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5C6DA4E-4B0C-4AE4-BA21-ACC51AAB6F30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5467BE30-40A5-4F7E-9AAF-F1BCDB24E85B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3672" yWindow="6336" windowWidth="21084" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6780" yWindow="8595" windowWidth="28800" windowHeight="15435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="施工干扰" sheetId="1" r:id="rId1"/>
+    <sheet name="2023-07-05" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
-  <si>
-    <t>层级编码</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>父级编码</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+  <si>
+    <t>层级码</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1-1-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2-2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>通用条件编码</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>条件名称</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>条件内容</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
@@ -75,12 +95,12 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <color indexed="8"/>
       <name val="宋体"/>
-      <family val="2"/>
+      <family val="3"/>
       <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -126,20 +146,26 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -417,39 +443,68 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="4" width="16.6640625" customWidth="1"/>
-    <col min="5" max="5" width="22.109375" customWidth="1"/>
+    <col min="1" max="1" width="9" style="5"/>
+    <col min="2" max="2" width="15.125" customWidth="1"/>
+    <col min="3" max="3" width="16.5" customWidth="1"/>
+    <col min="4" max="4" width="17.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:4" ht="16.5" x14ac:dyDescent="0.15">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="13.9" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="5">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="B2" s="3"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="3"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A3" s="6" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A4" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A5" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A6" s="6" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="4"/>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A7" s="6" t="s">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <dataValidations count="1">
+    <dataValidation showInputMessage="1" showErrorMessage="1" sqref="B1:B1048576" xr:uid="{8C7B18EB-1706-4693-9E43-8A9FE2C13F13}"/>
+  </dataValidations>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>